--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526636.1379149681</v>
+        <v>526636</v>
       </c>
       <c r="R2" t="n">
-        <v>6882928.915698895</v>
+        <v>6882929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2019-06-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>219790</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>219790</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>78528772</v>
       </c>
       <c r="B2" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78528772</v>
+        <v>78528747</v>
       </c>
       <c r="B2" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526636</v>
+        <v>526661</v>
       </c>
       <c r="R2" t="n">
-        <v>6882929</v>
+        <v>6882908</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Caspar Ström, Anders Granér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,12 +775,7 @@
         <v>78528725</v>
       </c>
       <c r="B3" t="n">
-        <v>92505</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526651.133576635</v>
+        <v>526651</v>
       </c>
       <c r="R3" t="n">
-        <v>6882931.845490674</v>
+        <v>6882932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,19 +840,9 @@
           <t>2019-06-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78528749</v>
+        <v>78528770</v>
       </c>
       <c r="B4" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526624.8893106068</v>
+        <v>526644</v>
       </c>
       <c r="R4" t="n">
-        <v>6882926.952703844</v>
+        <v>6882933</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,19 +937,9 @@
           <t>2019-06-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Caspar Ström, Anders Granér</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78528770</v>
+        <v>78528831</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526644.0829403419</v>
+        <v>526949</v>
       </c>
       <c r="R5" t="n">
-        <v>6882933.195954354</v>
+        <v>6882540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>78528747</v>
+        <v>78481512</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526661.1770769716</v>
+        <v>526699</v>
       </c>
       <c r="R6" t="n">
-        <v>6882908.023705732</v>
+        <v>6882341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-06-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,19 +1144,524 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gammal sälg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>78481631</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skarpen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>526706</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6882340</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gammal sälg</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78528769</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skarpen, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>526526</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6882960</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Caspar Ström</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>78528772</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skarpen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>526636</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6882929</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>78528749</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skarpen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>526625</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6882927</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Caspar Ström, Anders Granér</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>81838364</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skarpen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>527121</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6882934</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31524-2022 artfynd.xlsx
+++ b/artfynd/A 31524-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528747</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528725</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528770</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528831</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481631</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528769</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528772</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528749</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,8 +1712,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81838364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>